--- a/assetcore/public/import_templates/06_danh_sach_nguoi_dung.xlsx
+++ b/assetcore/public/import_templates/06_danh_sach_nguoi_dung.xlsx
@@ -527,26 +527,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 HƯỚNG DẪN IMPORT: Danh sách người dùng  |  Mỗi hàng = 1 người dùng. Email là định danh duy nhất — không trùng. Role Profile phải tồn tại trong hệ thống trước khi import.</t>
+          <t>📋 HƯỚNG DẪN IMPORT: Danh sách người dùng  |  Mỗi hàng = 1 người dùng. Email là định danh duy nhất. Nếu đã tồn tại sẽ cập nhật thông tin. Vai trò chỉ được thêm, không bao giờ xóa vai trò hiện có.</t>
         </is>
       </c>
     </row>
@@ -568,49 +564,29 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>mobile_no</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>mobile_no</t>
+          <t>ac_department</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>imm_approval_status</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>role_profile_name</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>send_welcome_email</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>time_zone</t>
+          <t>roles</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Email (đăng nhập) (*)</t>
+          <t>Email (Mã người dùng) (*)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -625,42 +601,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Họ và tên đầy đủ</t>
+          <t>Điện thoại</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Số điện thoại</t>
+          <t>Khoa/Phòng</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Khoa phòng</t>
+          <t>Trạng thái duyệt</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Role Profile</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Gửi email chào mừng?</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>Tài khoản hoạt động</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Ngôn ngữ giao diện</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>Múi giờ</t>
+          <t>Vai trò (phân cách bằng dấu phẩy)</t>
         </is>
       </c>
     </row>
@@ -682,43 +638,22 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Họ và tên đầy đủ. Nếu để trống sẽ tự ghép họ + tên.</t>
+          <t>Số di động. VD: 0912345678.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Số di động. VD: 0912345678.</t>
+          <t>Mã khoa/phòng (AC Department name). VD: Khoa-HSTC.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Tên khoa phòng (khớp file 01 / sheet 'Khoa phòng').</t>
+          <t>Trạng thái duyệt IMM. Chọn: Pending / Approved / Rejected.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Tên Role Profile trong hệ thống. Xem danh sách roles với admin.
-VD: HTM Technician, HTM Manager, Department Head, Viewer.</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>1 = gửi email mật khẩu tạm cho user; 0 = không gửi.</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>1 = active (mặc định); 0 = disable ngay khi import.</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Mã ngôn ngữ. VD: vi (Tiếng Việt), en (English).</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Múi giờ. Mặc định: Asia/Ho_Chi_Minh.</t>
+          <t>Danh sách vai trò Frappe, phân cách bằng dấu phẩy. Chỉ thêm, không xóa vai trò hiện có. VD: HTM Technician, HTM Manager.</t>
         </is>
       </c>
     </row>
@@ -740,42 +675,22 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Nguyễn Văn A</t>
+          <t>0912345678</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>Khoa-HSTC</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Phòng Vật tư thiết bị</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>HTM Technician</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>vi</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>Asia/Ho_Chi_Minh</t>
+          <t>HTM Technician, HTM Manager</t>
         </is>
       </c>
     </row>
@@ -787,10 +702,6 @@
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="8" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="9" t="n"/>
@@ -800,10 +711,6 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="9" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="8" t="n"/>
@@ -813,10 +720,6 @@
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="9" t="n"/>
@@ -826,10 +729,6 @@
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="8" t="n"/>
@@ -839,10 +738,6 @@
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="8" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="9" t="n"/>
@@ -852,10 +747,6 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="8" t="n"/>
@@ -865,10 +756,6 @@
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="8" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="9" t="n"/>
@@ -878,10 +765,6 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="8" t="n"/>
@@ -891,10 +774,6 @@
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
-      <c r="K14" s="8" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="9" t="n"/>
@@ -904,10 +783,6 @@
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="8" t="n"/>
@@ -917,10 +792,6 @@
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="8" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="9" t="n"/>
@@ -930,10 +801,6 @@
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="8" t="n"/>
@@ -943,10 +810,6 @@
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="9" t="n"/>
@@ -956,10 +819,6 @@
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="8" t="n"/>
@@ -969,10 +828,6 @@
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="9" t="n"/>
@@ -982,10 +837,6 @@
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="8" t="n"/>
@@ -995,10 +846,6 @@
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="9" t="n"/>
@@ -1008,10 +855,6 @@
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="8" t="n"/>
@@ -1021,10 +864,6 @@
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="9" t="n"/>
@@ -1034,10 +873,6 @@
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="8" t="n"/>
@@ -1047,10 +882,6 @@
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="9" t="n"/>
@@ -1060,10 +891,6 @@
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="9" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="8" t="n"/>
@@ -1073,10 +900,6 @@
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="8" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="9" t="n"/>
@@ -1086,10 +909,6 @@
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="9" t="n"/>
       <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="8" t="n"/>
@@ -1099,10 +918,6 @@
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="8" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="9" t="n"/>
@@ -1112,10 +927,6 @@
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="9" t="n"/>
       <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="9" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="8" t="n"/>
@@ -1125,10 +936,6 @@
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="8" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="9" t="n"/>
@@ -1138,10 +945,6 @@
       <c r="E33" s="9" t="n"/>
       <c r="F33" s="9" t="n"/>
       <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="8" t="n"/>
@@ -1151,10 +954,6 @@
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="9" t="n"/>
@@ -1164,10 +963,6 @@
       <c r="E35" s="9" t="n"/>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="9" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="8" t="n"/>
@@ -1177,10 +972,6 @@
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="9" t="n"/>
@@ -1190,10 +981,6 @@
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="9" t="n"/>
       <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="9" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="8" t="n"/>
@@ -1203,10 +990,6 @@
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="9" t="n"/>
@@ -1216,10 +999,6 @@
       <c r="E39" s="9" t="n"/>
       <c r="F39" s="9" t="n"/>
       <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="8" t="n"/>
@@ -1229,10 +1008,6 @@
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="9" t="n"/>
@@ -1242,10 +1017,6 @@
       <c r="E41" s="9" t="n"/>
       <c r="F41" s="9" t="n"/>
       <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="8" t="n"/>
@@ -1255,10 +1026,6 @@
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="9" t="n"/>
@@ -1268,10 +1035,6 @@
       <c r="E43" s="9" t="n"/>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="9" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="8" t="n"/>
@@ -1281,10 +1044,6 @@
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="9" t="n"/>
@@ -1294,10 +1053,6 @@
       <c r="E45" s="9" t="n"/>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="9" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="8" t="n"/>
@@ -1307,10 +1062,6 @@
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="n"/>
-      <c r="J46" s="8" t="n"/>
-      <c r="K46" s="8" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="9" t="n"/>
@@ -1320,10 +1071,6 @@
       <c r="E47" s="9" t="n"/>
       <c r="F47" s="9" t="n"/>
       <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n"/>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
-      <c r="K47" s="9" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="8" t="n"/>
@@ -1333,10 +1080,6 @@
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
-      <c r="J48" s="8" t="n"/>
-      <c r="K48" s="8" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="9" t="n"/>
@@ -1346,10 +1089,6 @@
       <c r="E49" s="9" t="n"/>
       <c r="F49" s="9" t="n"/>
       <c r="G49" s="9" t="n"/>
-      <c r="H49" s="9" t="n"/>
-      <c r="I49" s="9" t="n"/>
-      <c r="J49" s="9" t="n"/>
-      <c r="K49" s="9" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="8" t="n"/>
@@ -1359,10 +1098,6 @@
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="8" t="n"/>
-      <c r="J50" s="8" t="n"/>
-      <c r="K50" s="8" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="9" t="n"/>
@@ -1372,10 +1107,6 @@
       <c r="E51" s="9" t="n"/>
       <c r="F51" s="9" t="n"/>
       <c r="G51" s="9" t="n"/>
-      <c r="H51" s="9" t="n"/>
-      <c r="I51" s="9" t="n"/>
-      <c r="J51" s="9" t="n"/>
-      <c r="K51" s="9" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="8" t="n"/>
@@ -1385,10 +1116,6 @@
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="8" t="n"/>
-      <c r="J52" s="8" t="n"/>
-      <c r="K52" s="8" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="9" t="n"/>
@@ -1398,10 +1125,6 @@
       <c r="E53" s="9" t="n"/>
       <c r="F53" s="9" t="n"/>
       <c r="G53" s="9" t="n"/>
-      <c r="H53" s="9" t="n"/>
-      <c r="I53" s="9" t="n"/>
-      <c r="J53" s="9" t="n"/>
-      <c r="K53" s="9" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="8" t="n"/>
@@ -1411,10 +1134,6 @@
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
-      <c r="J54" s="8" t="n"/>
-      <c r="K54" s="8" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="9" t="n"/>
@@ -1424,10 +1143,6 @@
       <c r="E55" s="9" t="n"/>
       <c r="F55" s="9" t="n"/>
       <c r="G55" s="9" t="n"/>
-      <c r="H55" s="9" t="n"/>
-      <c r="I55" s="9" t="n"/>
-      <c r="J55" s="9" t="n"/>
-      <c r="K55" s="9" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="8" t="n"/>
@@ -1437,10 +1152,6 @@
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
-      <c r="H56" s="8" t="n"/>
-      <c r="I56" s="8" t="n"/>
-      <c r="J56" s="8" t="n"/>
-      <c r="K56" s="8" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="9" t="n"/>
@@ -1450,10 +1161,6 @@
       <c r="E57" s="9" t="n"/>
       <c r="F57" s="9" t="n"/>
       <c r="G57" s="9" t="n"/>
-      <c r="H57" s="9" t="n"/>
-      <c r="I57" s="9" t="n"/>
-      <c r="J57" s="9" t="n"/>
-      <c r="K57" s="9" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="8" t="n"/>
@@ -1463,10 +1170,6 @@
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="8" t="n"/>
-      <c r="J58" s="8" t="n"/>
-      <c r="K58" s="8" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="9" t="n"/>
@@ -1476,10 +1179,6 @@
       <c r="E59" s="9" t="n"/>
       <c r="F59" s="9" t="n"/>
       <c r="G59" s="9" t="n"/>
-      <c r="H59" s="9" t="n"/>
-      <c r="I59" s="9" t="n"/>
-      <c r="J59" s="9" t="n"/>
-      <c r="K59" s="9" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="8" t="n"/>
@@ -1489,10 +1188,6 @@
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
-      <c r="I60" s="8" t="n"/>
-      <c r="J60" s="8" t="n"/>
-      <c r="K60" s="8" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="9" t="n"/>
@@ -1502,10 +1197,6 @@
       <c r="E61" s="9" t="n"/>
       <c r="F61" s="9" t="n"/>
       <c r="G61" s="9" t="n"/>
-      <c r="H61" s="9" t="n"/>
-      <c r="I61" s="9" t="n"/>
-      <c r="J61" s="9" t="n"/>
-      <c r="K61" s="9" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="8" t="n"/>
@@ -1515,10 +1206,6 @@
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="8" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="9" t="n"/>
@@ -1528,10 +1215,6 @@
       <c r="E63" s="9" t="n"/>
       <c r="F63" s="9" t="n"/>
       <c r="G63" s="9" t="n"/>
-      <c r="H63" s="9" t="n"/>
-      <c r="I63" s="9" t="n"/>
-      <c r="J63" s="9" t="n"/>
-      <c r="K63" s="9" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="8" t="n"/>
@@ -1541,10 +1224,6 @@
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-      <c r="J64" s="8" t="n"/>
-      <c r="K64" s="8" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="9" t="n"/>
@@ -1554,10 +1233,6 @@
       <c r="E65" s="9" t="n"/>
       <c r="F65" s="9" t="n"/>
       <c r="G65" s="9" t="n"/>
-      <c r="H65" s="9" t="n"/>
-      <c r="I65" s="9" t="n"/>
-      <c r="J65" s="9" t="n"/>
-      <c r="K65" s="9" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="8" t="n"/>
@@ -1567,10 +1242,6 @@
       <c r="E66" s="8" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
-      <c r="I66" s="8" t="n"/>
-      <c r="J66" s="8" t="n"/>
-      <c r="K66" s="8" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="9" t="n"/>
@@ -1580,10 +1251,6 @@
       <c r="E67" s="9" t="n"/>
       <c r="F67" s="9" t="n"/>
       <c r="G67" s="9" t="n"/>
-      <c r="H67" s="9" t="n"/>
-      <c r="I67" s="9" t="n"/>
-      <c r="J67" s="9" t="n"/>
-      <c r="K67" s="9" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="8" t="n"/>
@@ -1593,10 +1260,6 @@
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
-      <c r="I68" s="8" t="n"/>
-      <c r="J68" s="8" t="n"/>
-      <c r="K68" s="8" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="9" t="n"/>
@@ -1606,10 +1269,6 @@
       <c r="E69" s="9" t="n"/>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="9" t="n"/>
-      <c r="H69" s="9" t="n"/>
-      <c r="I69" s="9" t="n"/>
-      <c r="J69" s="9" t="n"/>
-      <c r="K69" s="9" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="8" t="n"/>
@@ -1619,10 +1278,6 @@
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
-      <c r="H70" s="8" t="n"/>
-      <c r="I70" s="8" t="n"/>
-      <c r="J70" s="8" t="n"/>
-      <c r="K70" s="8" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="9" t="n"/>
@@ -1632,10 +1287,6 @@
       <c r="E71" s="9" t="n"/>
       <c r="F71" s="9" t="n"/>
       <c r="G71" s="9" t="n"/>
-      <c r="H71" s="9" t="n"/>
-      <c r="I71" s="9" t="n"/>
-      <c r="J71" s="9" t="n"/>
-      <c r="K71" s="9" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="8" t="n"/>
@@ -1645,10 +1296,6 @@
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
-      <c r="H72" s="8" t="n"/>
-      <c r="I72" s="8" t="n"/>
-      <c r="J72" s="8" t="n"/>
-      <c r="K72" s="8" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="9" t="n"/>
@@ -1658,10 +1305,6 @@
       <c r="E73" s="9" t="n"/>
       <c r="F73" s="9" t="n"/>
       <c r="G73" s="9" t="n"/>
-      <c r="H73" s="9" t="n"/>
-      <c r="I73" s="9" t="n"/>
-      <c r="J73" s="9" t="n"/>
-      <c r="K73" s="9" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="8" t="n"/>
@@ -1671,10 +1314,6 @@
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
-      <c r="I74" s="8" t="n"/>
-      <c r="J74" s="8" t="n"/>
-      <c r="K74" s="8" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="9" t="n"/>
@@ -1684,10 +1323,6 @@
       <c r="E75" s="9" t="n"/>
       <c r="F75" s="9" t="n"/>
       <c r="G75" s="9" t="n"/>
-      <c r="H75" s="9" t="n"/>
-      <c r="I75" s="9" t="n"/>
-      <c r="J75" s="9" t="n"/>
-      <c r="K75" s="9" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="8" t="n"/>
@@ -1697,10 +1332,6 @@
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="n"/>
-      <c r="I76" s="8" t="n"/>
-      <c r="J76" s="8" t="n"/>
-      <c r="K76" s="8" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="9" t="n"/>
@@ -1710,10 +1341,6 @@
       <c r="E77" s="9" t="n"/>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="9" t="n"/>
-      <c r="H77" s="9" t="n"/>
-      <c r="I77" s="9" t="n"/>
-      <c r="J77" s="9" t="n"/>
-      <c r="K77" s="9" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="8" t="n"/>
@@ -1723,10 +1350,6 @@
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="8" t="n"/>
-      <c r="J78" s="8" t="n"/>
-      <c r="K78" s="8" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="9" t="n"/>
@@ -1736,10 +1359,6 @@
       <c r="E79" s="9" t="n"/>
       <c r="F79" s="9" t="n"/>
       <c r="G79" s="9" t="n"/>
-      <c r="H79" s="9" t="n"/>
-      <c r="I79" s="9" t="n"/>
-      <c r="J79" s="9" t="n"/>
-      <c r="K79" s="9" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="8" t="n"/>
@@ -1749,10 +1368,6 @@
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
-      <c r="H80" s="8" t="n"/>
-      <c r="I80" s="8" t="n"/>
-      <c r="J80" s="8" t="n"/>
-      <c r="K80" s="8" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="9" t="n"/>
@@ -1762,10 +1377,6 @@
       <c r="E81" s="9" t="n"/>
       <c r="F81" s="9" t="n"/>
       <c r="G81" s="9" t="n"/>
-      <c r="H81" s="9" t="n"/>
-      <c r="I81" s="9" t="n"/>
-      <c r="J81" s="9" t="n"/>
-      <c r="K81" s="9" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="8" t="n"/>
@@ -1775,10 +1386,6 @@
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="n"/>
-      <c r="I82" s="8" t="n"/>
-      <c r="J82" s="8" t="n"/>
-      <c r="K82" s="8" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="9" t="n"/>
@@ -1788,10 +1395,6 @@
       <c r="E83" s="9" t="n"/>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="9" t="n"/>
-      <c r="H83" s="9" t="n"/>
-      <c r="I83" s="9" t="n"/>
-      <c r="J83" s="9" t="n"/>
-      <c r="K83" s="9" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="8" t="n"/>
@@ -1801,10 +1404,6 @@
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
-      <c r="I84" s="8" t="n"/>
-      <c r="J84" s="8" t="n"/>
-      <c r="K84" s="8" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="9" t="n"/>
@@ -1814,10 +1413,6 @@
       <c r="E85" s="9" t="n"/>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="9" t="n"/>
-      <c r="H85" s="9" t="n"/>
-      <c r="I85" s="9" t="n"/>
-      <c r="J85" s="9" t="n"/>
-      <c r="K85" s="9" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="8" t="n"/>
@@ -1827,10 +1422,6 @@
       <c r="E86" s="8" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="n"/>
-      <c r="I86" s="8" t="n"/>
-      <c r="J86" s="8" t="n"/>
-      <c r="K86" s="8" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="9" t="n"/>
@@ -1840,10 +1431,6 @@
       <c r="E87" s="9" t="n"/>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="9" t="n"/>
-      <c r="H87" s="9" t="n"/>
-      <c r="I87" s="9" t="n"/>
-      <c r="J87" s="9" t="n"/>
-      <c r="K87" s="9" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="8" t="n"/>
@@ -1853,10 +1440,6 @@
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="n"/>
-      <c r="I88" s="8" t="n"/>
-      <c r="J88" s="8" t="n"/>
-      <c r="K88" s="8" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="9" t="n"/>
@@ -1866,10 +1449,6 @@
       <c r="E89" s="9" t="n"/>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="9" t="n"/>
-      <c r="H89" s="9" t="n"/>
-      <c r="I89" s="9" t="n"/>
-      <c r="J89" s="9" t="n"/>
-      <c r="K89" s="9" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="8" t="n"/>
@@ -1879,10 +1458,6 @@
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="n"/>
-      <c r="I90" s="8" t="n"/>
-      <c r="J90" s="8" t="n"/>
-      <c r="K90" s="8" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="9" t="n"/>
@@ -1892,10 +1467,6 @@
       <c r="E91" s="9" t="n"/>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="9" t="n"/>
-      <c r="H91" s="9" t="n"/>
-      <c r="I91" s="9" t="n"/>
-      <c r="J91" s="9" t="n"/>
-      <c r="K91" s="9" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="8" t="n"/>
@@ -1905,10 +1476,6 @@
       <c r="E92" s="8" t="n"/>
       <c r="F92" s="8" t="n"/>
       <c r="G92" s="8" t="n"/>
-      <c r="H92" s="8" t="n"/>
-      <c r="I92" s="8" t="n"/>
-      <c r="J92" s="8" t="n"/>
-      <c r="K92" s="8" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="9" t="n"/>
@@ -1918,10 +1485,6 @@
       <c r="E93" s="9" t="n"/>
       <c r="F93" s="9" t="n"/>
       <c r="G93" s="9" t="n"/>
-      <c r="H93" s="9" t="n"/>
-      <c r="I93" s="9" t="n"/>
-      <c r="J93" s="9" t="n"/>
-      <c r="K93" s="9" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="8" t="n"/>
@@ -1931,10 +1494,6 @@
       <c r="E94" s="8" t="n"/>
       <c r="F94" s="8" t="n"/>
       <c r="G94" s="8" t="n"/>
-      <c r="H94" s="8" t="n"/>
-      <c r="I94" s="8" t="n"/>
-      <c r="J94" s="8" t="n"/>
-      <c r="K94" s="8" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="9" t="n"/>
@@ -1944,10 +1503,6 @@
       <c r="E95" s="9" t="n"/>
       <c r="F95" s="9" t="n"/>
       <c r="G95" s="9" t="n"/>
-      <c r="H95" s="9" t="n"/>
-      <c r="I95" s="9" t="n"/>
-      <c r="J95" s="9" t="n"/>
-      <c r="K95" s="9" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="8" t="n"/>
@@ -1957,10 +1512,6 @@
       <c r="E96" s="8" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
-      <c r="H96" s="8" t="n"/>
-      <c r="I96" s="8" t="n"/>
-      <c r="J96" s="8" t="n"/>
-      <c r="K96" s="8" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="9" t="n"/>
@@ -1970,10 +1521,6 @@
       <c r="E97" s="9" t="n"/>
       <c r="F97" s="9" t="n"/>
       <c r="G97" s="9" t="n"/>
-      <c r="H97" s="9" t="n"/>
-      <c r="I97" s="9" t="n"/>
-      <c r="J97" s="9" t="n"/>
-      <c r="K97" s="9" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="8" t="n"/>
@@ -1983,10 +1530,6 @@
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="n"/>
-      <c r="I98" s="8" t="n"/>
-      <c r="J98" s="8" t="n"/>
-      <c r="K98" s="8" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="9" t="n"/>
@@ -1996,10 +1539,6 @@
       <c r="E99" s="9" t="n"/>
       <c r="F99" s="9" t="n"/>
       <c r="G99" s="9" t="n"/>
-      <c r="H99" s="9" t="n"/>
-      <c r="I99" s="9" t="n"/>
-      <c r="J99" s="9" t="n"/>
-      <c r="K99" s="9" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="8" t="n"/>
@@ -2009,10 +1548,6 @@
       <c r="E100" s="8" t="n"/>
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="n"/>
-      <c r="I100" s="8" t="n"/>
-      <c r="J100" s="8" t="n"/>
-      <c r="K100" s="8" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="9" t="n"/>
@@ -2022,10 +1557,6 @@
       <c r="E101" s="9" t="n"/>
       <c r="F101" s="9" t="n"/>
       <c r="G101" s="9" t="n"/>
-      <c r="H101" s="9" t="n"/>
-      <c r="I101" s="9" t="n"/>
-      <c r="J101" s="9" t="n"/>
-      <c r="K101" s="9" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="8" t="n"/>
@@ -2035,10 +1566,6 @@
       <c r="E102" s="8" t="n"/>
       <c r="F102" s="8" t="n"/>
       <c r="G102" s="8" t="n"/>
-      <c r="H102" s="8" t="n"/>
-      <c r="I102" s="8" t="n"/>
-      <c r="J102" s="8" t="n"/>
-      <c r="K102" s="8" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="9" t="n"/>
@@ -2048,10 +1575,6 @@
       <c r="E103" s="9" t="n"/>
       <c r="F103" s="9" t="n"/>
       <c r="G103" s="9" t="n"/>
-      <c r="H103" s="9" t="n"/>
-      <c r="I103" s="9" t="n"/>
-      <c r="J103" s="9" t="n"/>
-      <c r="K103" s="9" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="8" t="n"/>
@@ -2061,10 +1584,6 @@
       <c r="E104" s="8" t="n"/>
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="8" t="n"/>
-      <c r="H104" s="8" t="n"/>
-      <c r="I104" s="8" t="n"/>
-      <c r="J104" s="8" t="n"/>
-      <c r="K104" s="8" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="9" t="n"/>
@@ -2074,21 +1593,14 @@
       <c r="E105" s="9" t="n"/>
       <c r="F105" s="9" t="n"/>
       <c r="G105" s="9" t="n"/>
-      <c r="H105" s="9" t="n"/>
-      <c r="I105" s="9" t="n"/>
-      <c r="J105" s="9" t="n"/>
-      <c r="K105" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="H5:H105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"1,0"</formula1>
-    </dataValidation>
-    <dataValidation sqref="I5:I105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"1,0"</formula1>
+  <dataValidations count="1">
+    <dataValidation sqref="F5:F105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Pending,Approved,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assetcore/public/import_templates/06_danh_sach_nguoi_dung.xlsx
+++ b/assetcore/public/import_templates/06_danh_sach_nguoi_dung.xlsx
@@ -542,7 +542,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 HƯỚNG DẪN IMPORT: Danh sách người dùng  |  Mỗi hàng = 1 người dùng. Email là định danh duy nhất. Nếu đã tồn tại sẽ cập nhật thông tin. Vai trò chỉ được thêm, không bao giờ xóa vai trò hiện có.</t>
+          <t>📋 HƯỚNG DẪN IMPORT: Danh sách người dùng  |  Mỗi hàng = 1 người dùng, điền từ HÀNG 6 (hàng 5 là ví dụ mẫu). Email là định danh duy nhất. Nếu đã tồn tại sẽ cập nhật thông tin. Khoa/Phòng điền TÊN, không điền mã. Vai trò chỉ được thêm, không bao giờ xóa vai trò hiện có.</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Email (Mã người dùng) (*)</t>
+          <t>Email đăng nhập (*)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Mã khoa/phòng (AC Department name). VD: Khoa-HSTC.</t>
+          <t>Tên khoa/phòng, khớp file 01 / sheet 'Khoa phòng'. Điền TÊN, KHÔNG điền mã hệ thống. Sai tên thì dòng vẫn nhập được nhưng để trống ô này.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái duyệt IMM. Chọn: Pending / Approved / Rejected.</t>
+          <t>Chờ xử lý / Đã phê duyệt / Bị từ chối.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -680,12 +680,12 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Khoa-HSTC</t>
+          <t>Khoa Hồi sức tích cực</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Đã phê duyệt</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1599,8 +1599,8 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"Pending,Approved,Rejected"</formula1>
+    <dataValidation sqref="F6:F105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Chờ xử lý,Đã phê duyệt,Bị từ chối"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assetcore/public/import_templates/06_danh_sach_nguoi_dung.xlsx
+++ b/assetcore/public/import_templates/06_danh_sach_nguoi_dung.xlsx
@@ -1599,7 +1599,7 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F6:F105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="F6:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Chờ xử lý,Đã phê duyệt,Bị từ chối"</formula1>
     </dataValidation>
   </dataValidations>
